--- a/04_Figures/F04_association/modules/T2/lm/c_data/results.xlsx
+++ b/04_Figures/F04_association/modules/T2/lm/c_data/results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t xml:space="preserve">outcome</t>
   </si>
@@ -69,12 +69,6 @@
   </si>
   <si>
     <t xml:space="preserve">ME_red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_salmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_tan</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise</t>
@@ -488,16 +482,16 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>1.27026351013538</v>
+        <v>2.51602672250863</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0823713905035618</v>
+        <v>0.102026147852122</v>
       </c>
       <c r="F2" t="n">
-        <v>0.935606168795604</v>
+        <v>0.920292845927038</v>
       </c>
       <c r="G2" t="n">
-        <v>0.99912855184111</v>
+        <v>0.992483956574485</v>
       </c>
     </row>
     <row r="3">
@@ -511,16 +505,16 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>18.3679262825966</v>
+        <v>5.65891316968641</v>
       </c>
       <c r="E3" t="n">
-        <v>0.881583769175973</v>
+        <v>0.331455500034601</v>
       </c>
       <c r="F3" t="n">
-        <v>0.394010042192901</v>
+        <v>0.745582924808945</v>
       </c>
       <c r="G3" t="n">
-        <v>0.966969620719842</v>
+        <v>0.992483956574485</v>
       </c>
     </row>
     <row r="4">
@@ -534,16 +528,16 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-7.48592302124221</v>
+        <v>22.4291177462794</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.351638873299194</v>
+        <v>1.26631382993342</v>
       </c>
       <c r="F4" t="n">
-        <v>0.730743217205334</v>
+        <v>0.227621510840048</v>
       </c>
       <c r="G4" t="n">
-        <v>0.966969620719842</v>
+        <v>0.992483956574485</v>
       </c>
     </row>
     <row r="5">
@@ -557,16 +551,16 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>8.74370589242519</v>
+        <v>-8.63626332563231</v>
       </c>
       <c r="E5" t="n">
-        <v>0.425746220520339</v>
+        <v>-0.463830635350382</v>
       </c>
       <c r="F5" t="n">
-        <v>0.677256685114821</v>
+        <v>0.650439897675493</v>
       </c>
       <c r="G5" t="n">
-        <v>0.966969620719842</v>
+        <v>0.992483956574485</v>
       </c>
     </row>
     <row r="6">
@@ -580,16 +574,16 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0190524795199135</v>
+        <v>-0.16458854109171</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00111338465072738</v>
+        <v>-0.00960284779147701</v>
       </c>
       <c r="F6" t="n">
-        <v>0.99912855184111</v>
+        <v>0.992483956574485</v>
       </c>
       <c r="G6" t="n">
-        <v>0.99912855184111</v>
+        <v>0.992483956574485</v>
       </c>
     </row>
     <row r="7">
@@ -603,16 +597,16 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>7.20674396445598</v>
+        <v>0.590987952176645</v>
       </c>
       <c r="E7" t="n">
-        <v>0.442836048831338</v>
+        <v>0.0380237150100889</v>
       </c>
       <c r="F7" t="n">
-        <v>0.665163509480471</v>
+        <v>0.970246484655667</v>
       </c>
       <c r="G7" t="n">
-        <v>0.966969620719842</v>
+        <v>0.992483956574485</v>
       </c>
     </row>
     <row r="8">
@@ -626,16 +620,16 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>22.8686640412455</v>
+        <v>14.6048372518541</v>
       </c>
       <c r="E8" t="n">
-        <v>1.28755952181359</v>
+        <v>0.6318016805442</v>
       </c>
       <c r="F8" t="n">
-        <v>0.220349596885269</v>
+        <v>0.538468777399908</v>
       </c>
       <c r="G8" t="n">
-        <v>0.966969620719842</v>
+        <v>0.992483956574485</v>
       </c>
     </row>
     <row r="9">
@@ -649,16 +643,16 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>1.49714102071905</v>
+        <v>29.9811522189119</v>
       </c>
       <c r="E9" t="n">
-        <v>0.071295851941518</v>
+        <v>1.51474868689189</v>
       </c>
       <c r="F9" t="n">
-        <v>0.944247461216619</v>
+        <v>0.153766185662585</v>
       </c>
       <c r="G9" t="n">
-        <v>0.99912855184111</v>
+        <v>0.992483956574485</v>
       </c>
     </row>
     <row r="10">
@@ -672,16 +666,16 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.58465268640682</v>
+        <v>20.0575005528173</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.340221158758406</v>
+        <v>0.96763113021822</v>
       </c>
       <c r="F10" t="n">
-        <v>0.739124627534103</v>
+        <v>0.350886725881326</v>
       </c>
       <c r="G10" t="n">
-        <v>0.966969620719842</v>
+        <v>0.992483956574485</v>
       </c>
     </row>
     <row r="11">
@@ -695,16 +689,16 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>3.63838643695044</v>
+        <v>-14.9317200878411</v>
       </c>
       <c r="E11" t="n">
-        <v>0.33384176178654</v>
+        <v>-0.910030120240738</v>
       </c>
       <c r="F11" t="n">
-        <v>0.743822785169109</v>
+        <v>0.379370492523498</v>
       </c>
       <c r="G11" t="n">
-        <v>0.966969620719842</v>
+        <v>0.992483956574485</v>
       </c>
     </row>
     <row r="12">
@@ -718,62 +712,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.4060631451297</v>
+        <v>-11.943645077654</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.588122762995582</v>
+        <v>-0.596414949162079</v>
       </c>
       <c r="F12" t="n">
-        <v>0.566527304559352</v>
+        <v>0.561140624828954</v>
       </c>
       <c r="G12" t="n">
-        <v>0.966969620719842</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-14.8714766201938</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.91355788787886</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.377581354560611</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.966969620719842</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>19.0742545683445</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.00555014508434</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.332982574260421</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.966969620719842</v>
+        <v>0.992483956574485</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +760,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -821,21 +769,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>2845.28115949455</v>
+        <v>4005.80380127198</v>
       </c>
       <c r="E2" t="n">
-        <v>1.14117487042872</v>
+        <v>0.99340717674377</v>
       </c>
       <c r="F2" t="n">
-        <v>0.274383556301778</v>
+        <v>0.338643080129284</v>
       </c>
       <c r="G2" t="n">
-        <v>0.549467775925825</v>
+        <v>0.465634235177766</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -844,21 +792,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>4232.85154088716</v>
+        <v>-2840.25928977039</v>
       </c>
       <c r="E3" t="n">
-        <v>1.22985754231659</v>
+        <v>-1.0151114206941</v>
       </c>
       <c r="F3" t="n">
-        <v>0.240543688479095</v>
+        <v>0.328573846173015</v>
       </c>
       <c r="G3" t="n">
-        <v>0.549467775925825</v>
+        <v>0.465634235177766</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -867,21 +815,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>1473.29239134566</v>
+        <v>3935.30008760995</v>
       </c>
       <c r="E4" t="n">
-        <v>0.408870936470451</v>
+        <v>1.31626583283687</v>
       </c>
       <c r="F4" t="n">
-        <v>0.689290110097119</v>
+        <v>0.210821481880083</v>
       </c>
       <c r="G4" t="n">
-        <v>0.748751199024556</v>
+        <v>0.465634235177766</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -890,21 +838,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-3361.27971116761</v>
+        <v>-1121.94165465669</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.99449322298235</v>
+        <v>-0.354202808363903</v>
       </c>
       <c r="F5" t="n">
-        <v>0.338134015954354</v>
+        <v>0.728865997392755</v>
       </c>
       <c r="G5" t="n">
-        <v>0.549467775925825</v>
+        <v>0.890836219035589</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -913,21 +861,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>3001.11423376834</v>
+        <v>2989.53923859455</v>
       </c>
       <c r="E6" t="n">
-        <v>1.07983018432194</v>
+        <v>1.07342278179063</v>
       </c>
       <c r="F6" t="n">
-        <v>0.299844907491818</v>
+        <v>0.302603117336966</v>
       </c>
       <c r="G6" t="n">
-        <v>0.549467775925825</v>
+        <v>0.465634235177766</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -936,21 +884,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>2236.25545185774</v>
+        <v>2764.60625003441</v>
       </c>
       <c r="E7" t="n">
-        <v>0.825256377397315</v>
+        <v>1.09653048121431</v>
       </c>
       <c r="F7" t="n">
-        <v>0.42411150707705</v>
+        <v>0.292744137364841</v>
       </c>
       <c r="G7" t="n">
-        <v>0.612605510222406</v>
+        <v>0.465634235177766</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -959,21 +907,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>5193.31326942309</v>
+        <v>5280.17159610488</v>
       </c>
       <c r="E8" t="n">
-        <v>1.81921580934055</v>
+        <v>1.42725391597278</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0919780031373697</v>
+        <v>0.177083615621433</v>
       </c>
       <c r="G8" t="n">
-        <v>0.549467775925825</v>
+        <v>0.465634235177766</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -982,21 +930,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>3965.08652786954</v>
+        <v>4250.63668421417</v>
       </c>
       <c r="E9" t="n">
-        <v>1.17074570581712</v>
+        <v>1.23436594484401</v>
       </c>
       <c r="F9" t="n">
-        <v>0.262714832858401</v>
+        <v>0.238914938342844</v>
       </c>
       <c r="G9" t="n">
-        <v>0.549467775925825</v>
+        <v>0.465634235177766</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1005,21 +953,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-1330.58154326978</v>
+        <v>370.917450820865</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.406266910154901</v>
+        <v>0.101978467932463</v>
       </c>
       <c r="F10" t="n">
-        <v>0.691154952945744</v>
+        <v>0.920329956684349</v>
       </c>
       <c r="G10" t="n">
-        <v>0.748751199024556</v>
+        <v>0.921587759734975</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1028,21 +976,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-1267.3001332104</v>
+        <v>-3427.56633244363</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.69553399325043</v>
+        <v>-1.26619703065389</v>
       </c>
       <c r="F11" t="n">
-        <v>0.498966207438299</v>
+        <v>0.22766201145339</v>
       </c>
       <c r="G11" t="n">
-        <v>0.648656069669789</v>
+        <v>0.465634235177766</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1051,62 +999,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-4140.5411666106</v>
+        <v>345.244752802804</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.65897954007376</v>
+        <v>0.100362588684478</v>
       </c>
       <c r="F12" t="n">
-        <v>0.121037981176124</v>
+        <v>0.921587759734975</v>
       </c>
       <c r="G12" t="n">
-        <v>0.549467775925825</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-3337.05908259367</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-1.23940696423876</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.23710408752507</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.549467775925825</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-54.4424055548615</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.0163064627672269</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.98723750866551</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.98723750866551</v>
+        <v>0.921587759734975</v>
       </c>
     </row>
   </sheetData>
@@ -1145,7 +1047,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1154,21 +1056,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>1450.83819771391</v>
+        <v>3770.78343859069</v>
       </c>
       <c r="E2" t="n">
-        <v>0.604686168838497</v>
+        <v>1.0061335505582</v>
       </c>
       <c r="F2" t="n">
-        <v>0.555795312322888</v>
+        <v>0.332712346033349</v>
       </c>
       <c r="G2" t="n">
-        <v>0.719943983803529</v>
+        <v>0.621262944364587</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1177,21 +1079,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>3715.00281860579</v>
+        <v>-2976.50537144082</v>
       </c>
       <c r="E3" t="n">
-        <v>1.15295788629844</v>
+        <v>-1.15593995254897</v>
       </c>
       <c r="F3" t="n">
-        <v>0.26968725043112</v>
+        <v>0.26850853197273</v>
       </c>
       <c r="G3" t="n">
-        <v>0.628010188647016</v>
+        <v>0.621262944364587</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1200,21 +1102,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>1485.59004563602</v>
+        <v>3362.79893084622</v>
       </c>
       <c r="E4" t="n">
-        <v>0.443687258943536</v>
+        <v>1.19669589668264</v>
       </c>
       <c r="F4" t="n">
-        <v>0.664563677357104</v>
+        <v>0.252793789726344</v>
       </c>
       <c r="G4" t="n">
-        <v>0.719943983803529</v>
+        <v>0.621262944364587</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1223,21 +1125,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-3597.06210650942</v>
+        <v>-1141.60607293574</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.15836434448934</v>
+        <v>-0.387794530995982</v>
       </c>
       <c r="F5" t="n">
-        <v>0.267553164419884</v>
+        <v>0.704443360576722</v>
       </c>
       <c r="G5" t="n">
-        <v>0.628010188647016</v>
+        <v>0.860986329593772</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1246,21 +1148,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>2183.62020625647</v>
+        <v>2235.41478997509</v>
       </c>
       <c r="E6" t="n">
-        <v>0.830249200617406</v>
+        <v>0.849590098202576</v>
       </c>
       <c r="F6" t="n">
-        <v>0.42138382612484</v>
+        <v>0.41092654299133</v>
       </c>
       <c r="G6" t="n">
-        <v>0.628010188647016</v>
+        <v>0.645741710414948</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1269,21 +1171,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>2033.95360210462</v>
+        <v>1407.43976119052</v>
       </c>
       <c r="E7" t="n">
-        <v>0.805933831306188</v>
+        <v>0.581536209831613</v>
       </c>
       <c r="F7" t="n">
-        <v>0.434776284447934</v>
+        <v>0.570825688792012</v>
       </c>
       <c r="G7" t="n">
-        <v>0.628010188647016</v>
+        <v>0.784885322089016</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1292,21 +1194,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>5071.5301319771</v>
+        <v>5387.62752990637</v>
       </c>
       <c r="E8" t="n">
-        <v>1.93500599032381</v>
+        <v>1.59097622613953</v>
       </c>
       <c r="F8" t="n">
-        <v>0.075048494320001</v>
+        <v>0.135629234709232</v>
       </c>
       <c r="G8" t="n">
-        <v>0.628010188647016</v>
+        <v>0.621262944364587</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1315,21 +1217,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>4069.00328499223</v>
+        <v>4062.85619178705</v>
       </c>
       <c r="E9" t="n">
-        <v>1.30651123443833</v>
+        <v>1.27243388094627</v>
       </c>
       <c r="F9" t="n">
-        <v>0.214021185539758</v>
+        <v>0.225507382508694</v>
       </c>
       <c r="G9" t="n">
-        <v>0.628010188647016</v>
+        <v>0.621262944364587</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1338,21 +1240,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>-1388.87399413294</v>
+        <v>632.533210042881</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.456604045668276</v>
+        <v>0.187118482045832</v>
       </c>
       <c r="F10" t="n">
-        <v>0.655491144688299</v>
+        <v>0.854456488256582</v>
       </c>
       <c r="G10" t="n">
-        <v>0.719943983803529</v>
+        <v>0.931335396672321</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1361,21 +1263,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-1583.50290742042</v>
+        <v>-2554.98110707804</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.948519764476729</v>
+        <v>-0.992921954411675</v>
       </c>
       <c r="F11" t="n">
-        <v>0.360165148024919</v>
+        <v>0.338870696926138</v>
       </c>
       <c r="G11" t="n">
-        <v>0.628010188647016</v>
+        <v>0.621262944364587</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1384,62 +1286,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-3474.34099229622</v>
+        <v>281.151536583308</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.46772241378521</v>
+        <v>0.08784916364929</v>
       </c>
       <c r="F12" t="n">
-        <v>0.165954158142683</v>
+        <v>0.931335396672321</v>
       </c>
       <c r="G12" t="n">
-        <v>0.628010188647016</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-2477.13447778745</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.96842212026653</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.350506388220756</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.628010188647016</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>126.504928300389</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.040732858387945</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.968127803168298</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.968127803168298</v>
+        <v>0.931335396672321</v>
       </c>
     </row>
   </sheetData>
@@ -1478,7 +1334,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1487,21 +1343,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-4.99332809048166</v>
+        <v>-8.53115765503709</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.64615125043081</v>
+        <v>-1.78494787109105</v>
       </c>
       <c r="F2" t="n">
-        <v>0.123680903365119</v>
+        <v>0.097609482330344</v>
       </c>
       <c r="G2" t="n">
-        <v>0.223076269713637</v>
+        <v>0.252455472982678</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1510,21 +1366,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.49673219389855</v>
+        <v>9.95923094627214</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.324102943583513</v>
+        <v>4.03012047779369</v>
       </c>
       <c r="F3" t="n">
-        <v>0.751015583011323</v>
+        <v>0.00142876685682359</v>
       </c>
       <c r="G3" t="n">
-        <v>0.864674710684184</v>
+        <v>0.0157164354250594</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1533,21 +1389,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-7.26827671813915</v>
+        <v>1.43335561203167</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.74662241637355</v>
+        <v>0.354908117596711</v>
       </c>
       <c r="F4" t="n">
-        <v>0.104270767793713</v>
+        <v>0.728349913962225</v>
       </c>
       <c r="G4" t="n">
-        <v>0.223076269713637</v>
+        <v>0.827718616399687</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1556,21 +1412,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>12.5378276194492</v>
+        <v>0.717911648152649</v>
       </c>
       <c r="E5" t="n">
-        <v>4.46268467753822</v>
+        <v>0.177117002313875</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000639557128434251</v>
+        <v>0.862146244843599</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00831424266964527</v>
+        <v>0.862146244843599</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1579,21 +1435,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-7.30032749410445</v>
+        <v>-7.31562781991828</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.35806198507625</v>
+        <v>-2.35972545171829</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0347005011008182</v>
+        <v>0.0345929905586103</v>
       </c>
       <c r="G6" t="n">
-        <v>0.10102427846149</v>
+        <v>0.190261448072357</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1602,21 +1458,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>0.61542894764067</v>
+        <v>-5.11997141402431</v>
       </c>
       <c r="E7" t="n">
-        <v>0.17383262568518</v>
+        <v>-1.68127680204935</v>
       </c>
       <c r="F7" t="n">
-        <v>0.864674710684184</v>
+        <v>0.116561668151419</v>
       </c>
       <c r="G7" t="n">
-        <v>0.864674710684184</v>
+        <v>0.252455472982678</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1625,21 +1481,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.995583735484616</v>
+        <v>-2.88236833713989</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.244757679596364</v>
+        <v>-0.575337429213774</v>
       </c>
       <c r="F8" t="n">
-        <v>0.810464990473844</v>
+        <v>0.574886831431632</v>
       </c>
       <c r="G8" t="n">
-        <v>0.864674710684184</v>
+        <v>0.790469393218494</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1648,21 +1504,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.58341869362152</v>
+        <v>3.41611752269233</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.58369757507726</v>
+        <v>0.751917953963692</v>
       </c>
       <c r="F9" t="n">
-        <v>0.137277704439161</v>
+        <v>0.465496932977408</v>
       </c>
       <c r="G9" t="n">
-        <v>0.223076269713637</v>
+        <v>0.73149518039307</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -1671,21 +1527,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>2.02945495316959</v>
+        <v>8.3560086349742</v>
       </c>
       <c r="E10" t="n">
-        <v>0.487315710638589</v>
+        <v>2.07901319452616</v>
       </c>
       <c r="F10" t="n">
-        <v>0.63414898165401</v>
+        <v>0.0579766201836527</v>
       </c>
       <c r="G10" t="n">
-        <v>0.864674710684184</v>
+        <v>0.212580940673393</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -1694,21 +1550,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>5.26890555325019</v>
+        <v>-1.17376303425614</v>
       </c>
       <c r="E11" t="n">
-        <v>2.83146052504363</v>
+        <v>-0.322135741017257</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0141509355918061</v>
+        <v>0.752471469454261</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0919810813467396</v>
+        <v>0.827718616399687</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -1717,62 +1573,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>6.7868883015215</v>
+        <v>-6.35607704402266</v>
       </c>
       <c r="E12" t="n">
-        <v>2.29726502182659</v>
+        <v>-1.58183202663709</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0388554917159578</v>
+        <v>0.137702985263279</v>
       </c>
       <c r="G12" t="n">
-        <v>0.10102427846149</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-1.35101189300051</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-0.374155480786427</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.714320338954935</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.864674710684184</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>8.44576160013637</v>
-      </c>
-      <c r="E14" t="n">
-        <v>2.37595319326253</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.0335607231390932</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.10102427846149</v>
+        <v>0.252455472982678</v>
       </c>
     </row>
   </sheetData>
@@ -1811,7 +1621,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" t="n">
         <v>15</v>
@@ -1820,21 +1630,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>33.8077801821538</v>
+        <v>147.327254415851</v>
       </c>
       <c r="E2" t="n">
-        <v>0.594725342632429</v>
+        <v>1.78382269464416</v>
       </c>
       <c r="F2" t="n">
-        <v>0.562235956430528</v>
+        <v>0.0977995086179026</v>
       </c>
       <c r="G2" t="n">
-        <v>0.730906743359686</v>
+        <v>0.268948648699232</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" t="n">
         <v>15</v>
@@ -1843,21 +1653,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>146.850997910061</v>
+        <v>-43.8557283506035</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1286659179702</v>
+        <v>-0.697543970686873</v>
       </c>
       <c r="F3" t="n">
-        <v>0.052978068127283</v>
+        <v>0.497748909639958</v>
       </c>
       <c r="G3" t="n">
-        <v>0.239142753900851</v>
+        <v>0.66783035005222</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" t="n">
         <v>15</v>
@@ -1866,21 +1676,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>53.1596961889409</v>
+        <v>96.3955483605173</v>
       </c>
       <c r="E4" t="n">
-        <v>0.677024230234364</v>
+        <v>1.4871147873839</v>
       </c>
       <c r="F4" t="n">
-        <v>0.510259063459564</v>
+        <v>0.160832827881982</v>
       </c>
       <c r="G4" t="n">
-        <v>0.730906743359686</v>
+        <v>0.35383222134036</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5" t="n">
         <v>15</v>
@@ -1889,21 +1699,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>-52.3511521357994</v>
+        <v>28.0623372507365</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.690061735436282</v>
+        <v>0.402704711870329</v>
       </c>
       <c r="F5" t="n">
-        <v>0.502289311722654</v>
+        <v>0.693709377143678</v>
       </c>
       <c r="G5" t="n">
-        <v>0.730906743359686</v>
+        <v>0.763080314858046</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" t="n">
         <v>15</v>
@@ -1912,21 +1722,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>93.6539871646666</v>
+        <v>103.768975178125</v>
       </c>
       <c r="E6" t="n">
-        <v>1.60368560763362</v>
+        <v>1.81466690867986</v>
       </c>
       <c r="F6" t="n">
-        <v>0.132791778132802</v>
+        <v>0.092708394917434</v>
       </c>
       <c r="G6" t="n">
-        <v>0.345258623145285</v>
+        <v>0.268948648699232</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B7" t="n">
         <v>15</v>
@@ -1935,21 +1745,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>25.8379273178472</v>
+        <v>35.4362579461373</v>
       </c>
       <c r="E7" t="n">
-        <v>0.424820624698046</v>
+        <v>0.619320059971221</v>
       </c>
       <c r="F7" t="n">
-        <v>0.677914363623894</v>
+        <v>0.546406650042725</v>
       </c>
       <c r="G7" t="n">
-        <v>0.774501765303304</v>
+        <v>0.66783035005222</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B8" t="n">
         <v>15</v>
@@ -1958,21 +1768,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>128.110104890569</v>
+        <v>177.949515576806</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1062103175575</v>
+        <v>2.45646702196177</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0551867893617348</v>
+        <v>0.0288600473268681</v>
       </c>
       <c r="G8" t="n">
-        <v>0.239142753900851</v>
+        <v>0.268948648699232</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B9" t="n">
         <v>15</v>
@@ -1981,21 +1791,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>143.149915442482</v>
+        <v>84.4532272987479</v>
       </c>
       <c r="E9" t="n">
-        <v>2.11574420226713</v>
+        <v>1.10123882459142</v>
       </c>
       <c r="F9" t="n">
-        <v>0.054238760545537</v>
+        <v>0.290765189524577</v>
       </c>
       <c r="G9" t="n">
-        <v>0.239142753900851</v>
+        <v>0.533069514128392</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
@@ -2004,21 +1814,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>26.962774436705</v>
+        <v>0.5990721902705</v>
       </c>
       <c r="E10" t="n">
-        <v>0.373323343476597</v>
+        <v>0.00747329809183198</v>
       </c>
       <c r="F10" t="n">
-        <v>0.714924706433819</v>
+        <v>0.994150693541871</v>
       </c>
       <c r="G10" t="n">
-        <v>0.774501765303304</v>
+        <v>0.994150693541871</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11" t="n">
         <v>15</v>
@@ -2027,21 +1837,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-53.2005089687761</v>
+        <v>-104.229363755286</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.39541487462747</v>
+        <v>-1.85432950146069</v>
       </c>
       <c r="F11" t="n">
-        <v>0.186270950834566</v>
+        <v>0.0865117955378935</v>
       </c>
       <c r="G11" t="n">
-        <v>0.403587060141561</v>
+        <v>0.268948648699232</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B12" t="n">
         <v>15</v>
@@ -2050,62 +1860,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>-53.9939811158472</v>
+        <v>53.4668862277463</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.920708178691638</v>
+        <v>0.719129251356548</v>
       </c>
       <c r="F12" t="n">
-        <v>0.373972893056808</v>
+        <v>0.484788292214661</v>
       </c>
       <c r="G12" t="n">
-        <v>0.694521087105501</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-100.811306172299</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-1.79550348889329</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.0958427883423163</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.311489062112528</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" t="n">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-3.65037000244219</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-0.0496330181173853</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.96116930821909</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.96116930821909</v>
+        <v>0.66783035005222</v>
       </c>
     </row>
   </sheetData>
@@ -2144,7 +1908,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -2153,21 +1917,21 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>-8.65840286843834</v>
+        <v>-18.5913213075394</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.685253693869733</v>
+        <v>-0.95202842046945</v>
       </c>
       <c r="F2" t="n">
-        <v>0.506205729487872</v>
+        <v>0.359865507094353</v>
       </c>
       <c r="G2" t="n">
-        <v>0.78125607399406</v>
+        <v>0.659753429672981</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3" t="n">
         <v>14</v>
@@ -2176,21 +1940,21 @@
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>-7.44627101290696</v>
+        <v>19.4834757054946</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.437983045375949</v>
+        <v>1.55521285455706</v>
       </c>
       <c r="F3" t="n">
-        <v>0.669178578416605</v>
+        <v>0.145862246594688</v>
       </c>
       <c r="G3" t="n">
-        <v>0.869932151941586</v>
+        <v>0.615014003366359</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -2199,21 +1963,21 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>-28.3284585930047</v>
+        <v>-1.24129089623775</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.88498626871546</v>
+        <v>-0.0823344185821949</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0838726668854905</v>
+        <v>0.935738204993666</v>
       </c>
       <c r="G4" t="n">
-        <v>0.546014850953762</v>
+        <v>0.939782696792247</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B5" t="n">
         <v>14</v>
@@ -2222,21 +1986,21 @@
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>24.0534741995972</v>
+        <v>-1.23831205873008</v>
       </c>
       <c r="E5" t="n">
-        <v>1.59749898908241</v>
+        <v>-0.0779090137475435</v>
       </c>
       <c r="F5" t="n">
-        <v>0.136137595075716</v>
+        <v>0.939184445132815</v>
       </c>
       <c r="G5" t="n">
-        <v>0.546014850953762</v>
+        <v>0.939782696792247</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B6" t="n">
         <v>14</v>
@@ -2245,21 +2009,21 @@
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-16.5701115127437</v>
+        <v>-15.5240312001011</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.20344951740289</v>
+        <v>-1.13248635466573</v>
       </c>
       <c r="F6" t="n">
-        <v>0.252006854286352</v>
+        <v>0.279551819711981</v>
       </c>
       <c r="G6" t="n">
-        <v>0.546014850953762</v>
+        <v>0.615014003366359</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B7" t="n">
         <v>14</v>
@@ -2268,21 +2032,21 @@
         <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-8.57975571845128</v>
+        <v>-9.05096428344026</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.629424365809033</v>
+        <v>-0.711289038526758</v>
       </c>
       <c r="F7" t="n">
-        <v>0.540869589688195</v>
+        <v>0.490501042394501</v>
       </c>
       <c r="G7" t="n">
-        <v>0.78125607399406</v>
+        <v>0.691913702990011</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B8" t="n">
         <v>14</v>
@@ -2291,21 +2055,21 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>10.6879984968909</v>
+        <v>12.6802746443697</v>
       </c>
       <c r="E8" t="n">
-        <v>0.724843890590727</v>
+        <v>0.690182344754813</v>
       </c>
       <c r="F8" t="n">
-        <v>0.482442918562128</v>
+        <v>0.503209965810917</v>
       </c>
       <c r="G8" t="n">
-        <v>0.78125607399406</v>
+        <v>0.691913702990011</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9" t="n">
         <v>14</v>
@@ -2314,21 +2078,21 @@
         <v>15</v>
       </c>
       <c r="D9" t="n">
-        <v>3.38242500673865</v>
+        <v>21.2795630304166</v>
       </c>
       <c r="E9" t="n">
-        <v>0.199535552917488</v>
+        <v>1.3160636210567</v>
       </c>
       <c r="F9" t="n">
-        <v>0.845185028602497</v>
+        <v>0.212738925748565</v>
       </c>
       <c r="G9" t="n">
-        <v>0.972953179451541</v>
+        <v>0.615014003366359</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B10" t="n">
         <v>14</v>
@@ -2337,21 +2101,21 @@
         <v>16</v>
       </c>
       <c r="D10" t="n">
-        <v>1.88582869301982</v>
+        <v>19.2306402940204</v>
       </c>
       <c r="E10" t="n">
-        <v>0.114059424163522</v>
+        <v>1.1607541608025</v>
       </c>
       <c r="F10" t="n">
-        <v>0.911076822073704</v>
+        <v>0.268313080967207</v>
       </c>
       <c r="G10" t="n">
-        <v>0.972953179451541</v>
+        <v>0.615014003366359</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
@@ -2360,21 +2124,21 @@
         <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>11.6802941193095</v>
+        <v>1.05003708113721</v>
       </c>
       <c r="E11" t="n">
-        <v>1.44624029152562</v>
+        <v>0.0771409544307301</v>
       </c>
       <c r="F11" t="n">
-        <v>0.173719467019148</v>
+        <v>0.939782696792247</v>
       </c>
       <c r="G11" t="n">
-        <v>0.546014850953762</v>
+        <v>0.939782696792247</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B12" t="n">
         <v>14</v>
@@ -2383,62 +2147,16 @@
         <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>16.1293030318287</v>
+        <v>-29.9943493589986</v>
       </c>
       <c r="E12" t="n">
-        <v>1.28321935823665</v>
+        <v>-2.19166042364013</v>
       </c>
       <c r="F12" t="n">
-        <v>0.223643929250973</v>
+        <v>0.0488622153348556</v>
       </c>
       <c r="G12" t="n">
-        <v>0.546014850953762</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.468347577628146</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.034618443457592</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.972953179451541</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.972953179451541</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" t="n">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>18.4815758447771</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.24663719950552</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.236316240507094</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.546014850953762</v>
+        <v>0.537484368683412</v>
       </c>
     </row>
   </sheetData>
@@ -2454,45 +2172,45 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
         <v>26</v>
-      </c>
-      <c r="B1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" t="s">
-        <v>28</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
       </c>
       <c r="E1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>30</v>
-      </c>
-      <c r="G1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
         <v>33</v>
-      </c>
-      <c r="B2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" t="s">
-        <v>35</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -2501,76 +2219,76 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>7.48592302124221</v>
+        <v>11.943645077654</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
         <v>33</v>
       </c>
-      <c r="B3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" t="s">
-        <v>35</v>
-      </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>10.6879984968909</v>
+        <v>15.5240312001011</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
         <v>33</v>
       </c>
-      <c r="B4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" t="s">
-        <v>35</v>
-      </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>53.2005089687761</v>
+        <v>84.4532272987479</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
         <v>33</v>
       </c>
-      <c r="B5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" t="s">
-        <v>35</v>
-      </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -2579,24 +2297,24 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3001.11423376834</v>
+        <v>2989.53923859455</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
         <v>33</v>
       </c>
-      <c r="B6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
-      </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -2605,33 +2323,33 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2183.62020625647</v>
+        <v>2554.98110707804</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
         <v>33</v>
       </c>
-      <c r="B7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" t="s">
-        <v>35</v>
-      </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>5.26890555325019</v>
+        <v>5.11997141402431</v>
       </c>
     </row>
   </sheetData>
